--- a/Decks/Spara.xlsx
+++ b/Decks/Spara.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64DE774-2C39-435B-9976-58130E1B26D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF30D5D-2BC6-4445-B34E-7D976C613256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{944147F2-0001-441C-AD21-D02E4373DFF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="112">
   <si>
     <t>Função</t>
   </si>
@@ -350,9 +350,6 @@
     <t>Chasm Skulker</t>
   </si>
   <si>
-    <t>Mana Leak</t>
-  </si>
-  <si>
     <t>Crufix, God of Horizons</t>
   </si>
   <si>
@@ -366,9 +363,6 @@
   </si>
   <si>
     <t>Mirrodin's Core</t>
-  </si>
-  <si>
-    <t>Abzan Falconeer</t>
   </si>
   <si>
     <t>Falco Spara, Pactweaver</t>
@@ -807,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -897,7 +891,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
         <v>95</v>
@@ -1542,10 +1536,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1692,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D60" t="s">
         <v>67</v>
@@ -2107,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D87" t="s">
         <v>80</v>
@@ -2134,10 +2128,10 @@
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D89" t="s">
         <v>87</v>
@@ -2194,10 +2188,10 @@
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D93" t="s">
         <v>90</v>
@@ -2257,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D97" t="s">
         <v>86</v>
@@ -2302,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D100" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
